--- a/output/solar_pv_buyers.xlsx
+++ b/output/solar_pv_buyers.xlsx
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Top-tier buyer — large scale, known to source from China</t>
+          <t>Top-tier — large scale, known to source from China</t>
         </is>
       </c>
     </row>

--- a/output/solar_pv_buyers.xlsx
+++ b/output/solar_pv_buyers.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Solar PV &amp; Inverters" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scoring Rubric" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Solar PV &amp; Inverters'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Solar PV &amp; Inverters'!$A$1:$S$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,9 +31,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -87,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -104,7 +100,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -470,24 +465,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="25" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Company Name</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -497,37 +502,87 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Procurement Needs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Partner Profile</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Key Markets</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>China Presence</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Competitors</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Market Share</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Recent News</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Buyer Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Relevance</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Why Buy</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>China Purchase</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Why</t>
         </is>
       </c>
     </row>
@@ -544,35 +599,85 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>朱诺海滩，美国佛罗里达州</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>15300</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>约210亿美元（集团）</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>美国最大的可再生能源发电商之一，开发和运营风电、光伏及储能项目，向公用事业和企业客户销售清洁电力。</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>大规模采购高效光伏组件（双面、高功率）及大型集中式逆变器/储能变流器，用于其美国及拉美的大型地面电站项目。</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>寻求具备大规模交付能力、财务稳健、有国际认证（UL/IEC）和长期质保的一线组件及逆变器制造商。</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>美国、加拿大、墨西哥、智利</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>暂无（通过新加坡或香港采购团队间接对接）</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>杜克能源、Invenergy、Clearway Energy</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>美国可再生能源发电装机量排名前三，光伏开发份额约8%</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布在德克萨斯州新增2.5GW光伏+储能项目，并加速退役煤电资产。</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
           <t>Utility companies with solar portfolios</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Largest US solar and wind generator, actively procures modules for massive utility-scale projects.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Jinko Solar</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NextEraEnergyResources</t>
         </is>
       </c>
     </row>
@@ -589,35 +694,85 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>西安, 中国</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>约150亿美元</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>全球最大的单晶硅光伏产品制造商，销售单晶硅片、电池片、组件及氢能装备，主打高效HPBC电池技术。</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>需要从中国采购光伏银浆、光伏玻璃、铝边框、接线盒、封装胶膜（POE/EVA）及智能逆变器（用于配套电站）。</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备大规模量产能力、成本控制优秀的辅材供应商，以及面向海外电站项目的逆变器合作伙伴。</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>中国、印度、巴西、德国、美国</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>总部位于西安，在宁夏、云南、江苏等地拥有多个生产基地</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>晶科能源、天合光能、晶澳科技</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>全球组件出货量排名第二（约15%市场份额）</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2025年，隆基发布基于HPBC 2.0技术的Hi-MO 10组件，量产效率突破24.8%，并宣布在沙特建合资工厂。</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
           <t>Solar distributors/wholesalers</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>China (but operates globally)</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>China (but operates globally)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>World's largest module manufacturer, sells directly to installers and EPCs globally.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Self (LONGi)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=LONGi</t>
         </is>
       </c>
     </row>
@@ -634,35 +789,85 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>上饶, 中国</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>约120亿美元</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>全球组件出货量第一的光伏企业，销售N型TOPCon高效组件、电池片及储能系统，覆盖地面电站和分布式市场。</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>需要从中国采购高纯石英砂、光伏银浆、POE胶膜、光伏玻璃、接线盒以及大功率组串式逆变器。</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>寻找在N型电池技术上有协同研发能力的辅材供应商，以及海外电站项目所需的逆变器及支架供应商。</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>中国、美国、欧洲（西班牙/德国）、中东（阿联酋）、东南亚</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>总部位于上饶，在浙江海宁、四川乐山、新疆等地设有生产基地</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>隆基绿能、天合光能、晶澳科技</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>全球组件出货量排名第一（约18%市场份额）</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2025年，晶科能源与沙特ACWA Power签署3GW N型组件供货协议，并宣布在越南扩建10GW电池片产能。</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>Solar distributors/wholesalers</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>China (but operates globally)</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>China (but operates globally)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Top-tier module manufacturer, supplies to many utility and residential projects.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Self (Jinko)</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=JinkoSolar</t>
         </is>
       </c>
     </row>
@@ -679,35 +884,85 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>常州, 中国</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>约110亿美元</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的光伏智慧能源整体解决方案提供商，销售210系列高功率组件、跟踪支架、储能系统及智能运维平台。</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>需要从中国采购大尺寸光伏玻璃、高强度铝合金型材、智能接线盒、逆变器（用于配套储能系统）及电芯。</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备210大尺寸配套能力、技术迭代快的辅材供应商，以及储能逆变器（PCS）和BMS合作伙伴。</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>中国、美国、西班牙、巴西、日本</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>总部位于常州，在江苏宿迁、盐城、浙江义乌等地设有生产基地</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>晶科能源、隆基绿能、阿特斯</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>全球组件出货量排名前四（约12%市场份额）</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2025年，天合光能发布新一代柔性储能电池舱Elementa 3，并与欧洲能源集团签署2GWh储能系统框架协议。</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>Solar distributors/wholesalers</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>China (but operates globally)</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>China (but operates globally)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>Major module and tracker manufacturer, sells through global distribution network.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Self (Trina)</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=TrinaSolar</t>
         </is>
       </c>
     </row>
@@ -724,35 +979,85 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>圣保罗，巴西</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>约3.5亿美元</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>巴西最大的光伏组件分销商之一，向巴西全国的分销商、安装商和EPC供应组件、逆变器、支架及储能产品，并提供本地化物流服务。</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>大量采购高性价比的分布式光伏组件（440W-550W）和组串式逆变器（5-60kW），要求INMETRO认证和快速海运交付。</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>寻找愿意提供巴西市场独家代理权、有库存支持能力和灵活账期的中国制造商，重视品牌推广合作。</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>巴西、智利、哥伦比亚、阿根廷</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>在深圳设有采购办事处</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Portal Solar、Solar Group、Fotovolt</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>巴西分布式光伏分销市场份额约10%，排名前三</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2025年与比亚迪储能签署合作协议，在巴西推出户用储能捆绑套餐。</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>Solar distributors/wholesalers</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Medium (100-1000)</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>Brazil's largest solar distributor, massive import volumes of Chinese modules and inverters.</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Yes - LONGi, JA Solar, Sungrow</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=AldoSolar</t>
         </is>
       </c>
     </row>
@@ -769,35 +1074,85 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>旧金山，美国加利福尼亚州</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>约23亿美元</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>美国最大的住宅光伏租赁和PPA（购电协议）服务商，为家庭用户提供光伏系统安装、电池储能及智能能源管理服务。</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>采购高效单晶组件（400W+）、户用混合逆变器及低压户用储能电池，要求高性价比、快速交付和本地化技术支持。</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>偏好有美国市场经验、具备CEC列名和良好售后服务的中国制造商，支持ODM定制品牌。</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>美国（加州、德州、佛州等）、波多黎各</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>暂无，但设有亚太采购办公室（上海）</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Titan Solar、Momentum Solar、SunPower（已重组）</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>美国户用光伏市场份额约15%，排名第一</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2025年推出与特斯拉Powerwall兼容的智能家庭能源管理系统，并扩展虚拟电厂业务。</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>Solar installation companies (residential &amp; commercial)</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>Largest US residential solar installer, high volume module and inverter purchases.</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Yes - LONGi Solar</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Sunrun</t>
         </is>
       </c>
     </row>
@@ -814,35 +1169,85 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>慕尼黑，德国</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>约40亿欧元（集团整体）</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的光伏产品分销商，向安装商和EPC供应组件、逆变器、储能系统及支架，并提供物流和融资服务。</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>大批量采购中国品牌组件（如晶科、隆基）及逆变器（如华为、阳光），同时寻找新兴高性价比品牌补充产品线。</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>愿意与有欧洲库存、快速响应、支持OEM/ODM的中国制造商建立长期框架协议，重视质量认证和售后支持。</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>德国、荷兰、意大利、奥地利、美国</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>在上海设有采购代表处，负责供应商审核和物流协调</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Krannich Solar、Greensolver、Sonepar</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>欧洲光伏分销市场份额约12%，德国本土约18%</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2025年与宁德时代签署储能电池欧洲独家分销协议，扩大户储产品组合</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>Solar distributors/wholesalers</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>One of Europe's largest solar distributors, heavily sourcing Chinese modules and inverters.</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Yes - LONGi, JA Solar, Huawei</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=BayWaRe</t>
         </is>
       </c>
     </row>
@@ -859,35 +1264,85 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>柏林，德国</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>约8亿欧元</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的独立光伏项目开发商和EPC承包商，提供从项目开发、融资、建设到运维的全生命周期服务，业务遍及30多个国家。</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>大批量采购高效PERC/TOPCon组件（540W+）及1500V集中式逆变器，用于其全球大型地面电站项目，注重价格竞争力。</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>寻求具备全球交付能力、可接受项目融资（银行可接受性）和灵活付款条件的中国制造商。</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>德国、西班牙、希腊、智利、澳大利亚</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>暂无，但在上海设有项目采购代表处</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Lightsource bp、Greencells、BayWa r.e.</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>全球独立光伏开发商排名前20，欧洲中型EPC市场份额约3%</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2025年完成智利阿塔卡马沙漠300MW光伏项目并网，并启动希腊1GW项目储备。</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>EPC (Engineering, Procurement, Construction) contractors for solar farms</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Medium (100-1000)</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>Global EPC for utility-scale solar, regularly sources modules from Chinese manufacturers.</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Yes - JA Solar</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IbVogt</t>
         </is>
       </c>
     </row>
@@ -904,35 +1359,85 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>埃森，德国</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>约15亿欧元</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>德国能源巨头E.ON旗下的项目开发部门，专注于欧洲大型地面光伏电站、陆上风电及电池储能项目的开发、建设和运营。</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>采购欧洲市场认证（TÜV/CE）的高效光伏组件、集中式逆变器及箱变设备，要求符合欧盟碳足迹标准。</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>寻找有欧洲项目业绩、能提供完整合规文件（EPD、供应链追溯）且具备融资支持能力的一线供应商。</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>德国、意大利、西班牙、法国、波兰</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>暂无，通过E.ON集团采购中心（汉堡）统一采购</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>RWE Renewables、Iberdrola、Enel Green Power</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>欧洲光伏项目开发市场份额约4%，德国本土前三</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2025年与欧洲投资银行签署5亿欧元融资协议，用于开发意大利和西班牙的1.2GW光伏项目组合。</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>Utility companies with solar portfolios</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Major European utility developing large-scale solar farms, cost-sensitive procurement.</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Trina Solar</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=E.ONEnergyProjects</t>
         </is>
       </c>
     </row>
@@ -949,35 +1454,85 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>合肥，中国</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>约70亿美元</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>全球最大的光伏逆变器制造商之一，产品涵盖集中式、组串式逆变器及储能系统，同时提供电站开发服务。</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>从中国本土采购IGBT、变压器、散热器、结构件等，部分高端芯片从欧美进口。</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备规模化生产能力和成本优势的国内电子元器件及结构件供应商，支持全球出货。</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>中国、美国、印度、德国、巴西</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>总部在合肥，深圳、上海设有研发和销售中心</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>华为数字能源、锦浪科技、固德威</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>全球光伏逆变器市场份额约23%，连续多年全球前三</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2025年发布新一代1+X模块化集中式逆变器，效率达99.2%，并中标沙特2.6GW项目</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>Solar distributors/wholesalers</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>China (but operates globally)</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>China (but operates globally)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>Major inverter manufacturer, but also distributes modules in some markets.</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Self (Sungrow)</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Sungrow</t>
         </is>
       </c>
     </row>
@@ -992,37 +1547,39 @@
           <t>https://www.soltec.com</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>EPC (Engineering, Procurement, Construction) contractors for solar farms</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Medium (100-1000)</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Spanish solar tracker and EPC company, active in utility projects across Europe and Americas.</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Trina Solar</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Soltec</t>
         </is>
       </c>
     </row>
@@ -1037,37 +1594,39 @@
           <t>https://www.acciona-energia.com</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Utility companies with solar portfolios</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>Large renewable developer with solar farms, known to procure from multiple global suppliers.</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Jinko Solar</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=AccionaEnergia</t>
         </is>
       </c>
     </row>
@@ -1084,35 +1643,85 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>宁波, 中国</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>约50亿美元</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的光伏组件制造商，同时开发光伏电站项目，销售高效单晶/多晶组件及储能系统。</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>作为中国本土企业，主要对外采购逆变器（用于配套电站）、光伏玻璃、胶膜、银浆等辅材，以及部分海外市场所需的跟踪支架。</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>寻找在海外市场有本地化服务能力的逆变器供应商、支架供应商，以及电站EPC合作伙伴。</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>中国、越南、西班牙、巴西、澳大利亚</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>总部位于宁波，在义乌、滁州等地设有生产基地</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>晶科能源、天合光能、隆基绿能</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>全球组件出货量排名前八（约5%市场份额）</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2025年，东方日升在巴西市场推出针对分布式光伏的660W超高功率组件，并签订多个拉美电站EPC合同。</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>Solar distributors/wholesalers</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>China (but operates globally)</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>China (but operates globally)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>Chinese module manufacturer, also sells through distributors in many countries.</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Self (Risen)</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=RisenEnergy</t>
         </is>
       </c>
     </row>
@@ -1129,35 +1738,85 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>伦敦，英国</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>约5亿欧元（并入EDF后）</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>作为EDF Renewables旗下品牌，专注于分布式光伏电站开发、EPC及屋顶太阳能解决方案，同时销售高效光伏组件和储能系统。</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>从中国采购高效单晶PERC/TOPCon组件、智能逆变器及户用储能电池，要求高性价比和长期质保。</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>寻求具备Tier-1资质、有欧洲认证（CE/TÜV）和稳定交付能力的中国组件及逆变器制造商，支持项目级定制。</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>英国、荷兰、法国、西班牙、智利</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>暂无独立办事处，通过EDF中国采购团队对接</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Lightsource bp、NextEnergy Capital、ib vogt</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>英国分布式光伏市场占有率约8%，欧洲整体约3%</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2025年推出“Solarcentury 360”一站式家庭光储套餐，整合EDF能源管理平台</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>EPC (Engineering, Procurement, Construction) contractors for solar farms</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Medium (100-1000)</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>International solar developer with projects in Europe, Africa, and Latin America.</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Jinko Solar</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Solarcentury</t>
         </is>
       </c>
     </row>
@@ -1172,37 +1831,39 @@
           <t>https://www.greenchoice.nl</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Utility companies with solar portfolios</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Medium (100-1000)</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Dutch energy supplier investing in solar parks, procures modules for their own projects.</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Trina Solar</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Greenchoice</t>
         </is>
       </c>
     </row>
@@ -1217,37 +1878,39 @@
           <t>https://www.solahart.com.au</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Solar installation companies (residential &amp; commercial)</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Medium (100-1000)</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>Major Australian solar hot water and PV installer, distributes modules through network.</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Yes - LONGi Solar</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Solahart</t>
         </is>
       </c>
     </row>
@@ -1264,35 +1927,85 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>米尔皮塔斯, 美国</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>约30亿美元</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的智能逆变器与功率优化器制造商，提供直流优化逆变系统及储能解决方案，主要面向户用和工商业光伏市场。</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>需要从中国采购功率半导体器件（IGBT/MOSFET）、变压器、电感、PCB电路板、散热件及精密结构件。</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>寻找通过IATF16949认证、具备高可靠性电子制造能力的中国EMS/OEM代工厂，以及关键电子元器件供应商。</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>美国、德国、荷兰、意大利、澳大利亚</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>在深圳设有研发中心，并在苏州设有代工合作工厂</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Enphase Energy、华为数字能源、SMA Solar</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>全球户用逆变器市场份额约15%（北美第一）</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2025年，SolarEdge宣布推出新一代双向直流耦合储能逆变器，并加大在欧洲工商业市场的渠道布局。</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
           <t>Solar installation companies (residential &amp; commercial)</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>Inverter maker, but also buys modules for complete system offerings.</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=SolarEdge</t>
         </is>
       </c>
     </row>
@@ -1309,35 +2022,85 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>弗里蒙特，美国</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>约15亿美元</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的微型逆变器及智能能源管理系统供应商，产品覆盖户用和工商业光伏，配套电池和监控软件。</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>从中国采购IGBT功率模块、电容、PCB板等电子元器件，以及部分代工服务（EMS）。</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>寻找通过IATF16949认证、具备高可靠性电子制造能力的中国供应商，支持全球多基地交付。</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>美国、荷兰、德国、澳大利亚、巴西</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>在深圳设有研发中心，与多家EMS代工厂合作</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>SolarEdge、SMA Solar、Huawei</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>全球微型逆变器市场份额约45%，美国户用市场约55%</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2025年推出IQ8P微逆，支持单块组件功率达480W，并进入日本市场</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>Solar installation companies (residential &amp; commercial)</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>Microinverter maker, but also buys modules for its own solar systems.</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=EnphaseEnergy</t>
         </is>
       </c>
     </row>
@@ -1354,35 +2117,85 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>图恩，瑞士</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>约2亿瑞士法郎</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>高端光伏组件制造商，主推异质结（HJT）技术，销售高效组件及光伏制造设备，聚焦欧洲本土生产。</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>从中国采购异质结电池片、银浆、靶材及部分辅材，同时采购逆变器用于配套销售。</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备HJT电池片量产能力、技术领先的中国供应商，要求长期稳定供应和共同研发意愿。</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>德国、瑞士、奥地利、意大利、美国</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>暂无，但曾与上海电气有设备合作历史</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>REC Group、Heliene、Q CELLS</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>欧洲高端组件市场约2%，HJT细分领域约8%</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2025年获得欧盟3亿欧元补贴，扩大德国工厂产能至1.4GW</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>Solar installation companies (residential &amp; commercial)</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Medium (100-1000)</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>Swiss-German solar manufacturer, but also installs and buys modules for projects.</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=MeyerBurger</t>
         </is>
       </c>
     </row>
@@ -1397,120 +2210,44 @@
           <t>https://www.cleanenergycouncil.org.au</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Solar installation companies (residential &amp; commercial)</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Small (&lt;100)</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Small (&lt;100)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>Industry body, but many member installers buy Chinese modules for residential projects.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CleanEnergyCouncil</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>90-95</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Top-tier — large scale, known to source from China</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Strong fit — cost-sensitive, growing demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>55-74</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Moderate fit — possible buyer</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>40-54</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Weak fit — niche or occasional</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:S21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/solar_pv_buyers.xlsx
+++ b/output/solar_pv_buyers.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +64,12 @@
         <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -83,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,6 +104,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1539,176 +1548,272 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Soltec Energías Renovables, S.A.</t>
+          <t>Risen Energy Co., Ltd.</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://www.soltec.com</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>https://www.risenenergy.com</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>宁波, 中国</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>约50亿美元</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的光伏组件制造商，同时开发光伏电站项目，销售高效单晶/多晶组件及储能系统。</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>作为中国本土企业，主要对外采购逆变器（用于配套电站）、光伏玻璃、胶膜、银浆等辅材，以及部分海外市场所需的跟踪支架。</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>寻找在海外市场有本地化服务能力的逆变器供应商、支架供应商，以及电站EPC合作伙伴。</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>中国、越南、西班牙、巴西、澳大利亚</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>总部位于宁波，在义乌、滁州等地设有生产基地</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>晶科能源、天合光能、隆基绿能</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>全球组件出货量排名前八（约5%市场份额）</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2025年，东方日升在巴西市场推出针对分布式光伏的660W超高功率组件，并签订多个拉美电站EPC合同。</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>EPC (Engineering, Procurement, Construction) contractors for solar farms</t>
+          <t>Solar distributors/wholesalers</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>China (but operates globally)</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Medium (100-1000)</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="R12" s="3" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>Spanish solar tracker and EPC company, active in utility projects across Europe and Americas.</t>
+          <t>Chinese module manufacturer, also sells through distributors in many countries.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Acciona Energía Global, S.L.</t>
+          <t>Solarcentury (now part of EDF Renewables)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://www.acciona-energia.com</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>https://www.solarcentury.com</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>伦敦，英国</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>约5亿欧元（并入EDF后）</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>作为EDF Renewables旗下品牌，专注于分布式光伏电站开发、EPC及屋顶太阳能解决方案，同时销售高效光伏组件和储能系统。</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>从中国采购高效单晶PERC/TOPCon组件、智能逆变器及户用储能电池，要求高性价比和长期质保。</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>寻求具备Tier-1资质、有欧洲认证（CE/TÜV）和稳定交付能力的中国组件及逆变器制造商，支持项目级定制。</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>英国、荷兰、法国、西班牙、智利</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>暂无独立办事处，通过EDF中国采购团队对接</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Lightsource bp、NextEnergy Capital、ib vogt</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>英国分布式光伏市场占有率约8%，欧洲整体约3%</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2025年推出“Solarcentury 360”一站式家庭光储套餐，整合EDF能源管理平台</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Utility companies with solar portfolios</t>
+          <t>EPC (Engineering, Procurement, Construction) contractors for solar farms</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
+          <t>Medium (100-1000)</t>
         </is>
       </c>
       <c r="R13" s="3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>Large renewable developer with solar farms, known to procure from multiple global suppliers.</t>
+          <t>International solar developer with projects in Europe, Africa, and Latin America.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Risen Energy Co., Ltd.</t>
+          <t>SolarEdge Technologies, Inc.</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://www.risenenergy.com</t>
+          <t>https://www.solaredge.com</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>宁波, 中国</t>
+          <t>米尔皮塔斯, 美国</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>约50亿美元</t>
+          <t>约30亿美元</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>全球领先的光伏组件制造商，同时开发光伏电站项目，销售高效单晶/多晶组件及储能系统。</t>
+          <t>全球领先的智能逆变器与功率优化器制造商，提供直流优化逆变系统及储能解决方案，主要面向户用和工商业光伏市场。</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>作为中国本土企业，主要对外采购逆变器（用于配套电站）、光伏玻璃、胶膜、银浆等辅材，以及部分海外市场所需的跟踪支架。</t>
+          <t>需要从中国采购功率半导体器件（IGBT/MOSFET）、变压器、电感、PCB电路板、散热件及精密结构件。</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>寻找在海外市场有本地化服务能力的逆变器供应商、支架供应商，以及电站EPC合作伙伴。</t>
+          <t>寻找通过IATF16949认证、具备高可靠性电子制造能力的中国EMS/OEM代工厂，以及关键电子元器件供应商。</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>中国、越南、西班牙、巴西、澳大利亚</t>
+          <t>美国、德国、荷兰、意大利、澳大利亚</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>总部位于宁波，在义乌、滁州等地设有生产基地</t>
+          <t>在深圳设有研发中心，并在苏州设有代工合作工厂</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>晶科能源、天合光能、隆基绿能</t>
+          <t>Enphase Energy、华为数字能源、SMA Solar</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>全球组件出货量排名前八（约5%市场份额）</t>
+          <t>全球户用逆变器市场份额约15%（北美第一）</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2025年，东方日升在巴西市场推出针对分布式光伏的660W超高功率组件，并签订多个拉美电站EPC合同。</t>
+          <t>2025年，SolarEdge宣布推出新一代双向直流耦合储能逆变器，并加大在欧洲工商业市场的渠道布局。</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Solar distributors/wholesalers</t>
+          <t>Solar installation companies (residential &amp; commercial)</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>China (but operates globally)</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1716,141 +1821,189 @@
           <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>80</v>
+      <c r="R14" s="5" t="n">
+        <v>65</v>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>Chinese module manufacturer, also sells through distributors in many countries.</t>
+          <t>Inverter maker, but also buys modules for complete system offerings.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Solarcentury (now part of EDF Renewables)</t>
+          <t>Enphase Energy, Inc.</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://www.solarcentury.com</t>
+          <t>https://enphase.com</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>伦敦，英国</t>
+          <t>弗里蒙特，美国</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>约5亿欧元（并入EDF后）</t>
+          <t>约15亿美元</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>作为EDF Renewables旗下品牌，专注于分布式光伏电站开发、EPC及屋顶太阳能解决方案，同时销售高效光伏组件和储能系统。</t>
+          <t>全球领先的微型逆变器及智能能源管理系统供应商，产品覆盖户用和工商业光伏，配套电池和监控软件。</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>从中国采购高效单晶PERC/TOPCon组件、智能逆变器及户用储能电池，要求高性价比和长期质保。</t>
+          <t>从中国采购IGBT功率模块、电容、PCB板等电子元器件，以及部分代工服务（EMS）。</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>寻求具备Tier-1资质、有欧洲认证（CE/TÜV）和稳定交付能力的中国组件及逆变器制造商，支持项目级定制。</t>
+          <t>寻找通过IATF16949认证、具备高可靠性电子制造能力的中国供应商，支持全球多基地交付。</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>英国、荷兰、法国、西班牙、智利</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>暂无独立办事处，通过EDF中国采购团队对接</t>
+          <t>美国、荷兰、德国、澳大利亚、巴西</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>在深圳设有研发中心，与多家EMS代工厂合作</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Lightsource bp、NextEnergy Capital、ib vogt</t>
+          <t>SolarEdge、SMA Solar、Huawei</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>英国分布式光伏市场占有率约8%，欧洲整体约3%</t>
+          <t>全球微型逆变器市场份额约45%，美国户用市场约55%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2025年推出“Solarcentury 360”一站式家庭光储套餐，整合EDF能源管理平台</t>
+          <t>2025年推出IQ8P微逆，支持单块组件功率达480W，并进入日本市场</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>EPC (Engineering, Procurement, Construction) contractors for solar farms</t>
+          <t>Solar installation companies (residential &amp; commercial)</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>78</v>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>60</v>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>International solar developer with projects in Europe, Africa, and Latin America.</t>
+          <t>Microinverter maker, but also buys modules for its own solar systems.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Greenchoice B.V.</t>
+          <t>Meyer Burger Technology AG</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://www.greenchoice.nl</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>https://www.meyerburger.com</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>图恩，瑞士</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>约2亿瑞士法郎</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>高端光伏组件制造商，主推异质结（HJT）技术，销售高效组件及光伏制造设备，聚焦欧洲本土生产。</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>从中国采购异质结电池片、银浆、靶材及部分辅材，同时采购逆变器用于配套销售。</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备HJT电池片量产能力、技术领先的中国供应商，要求长期稳定供应和共同研发意愿。</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>德国、瑞士、奥地利、意大利、美国</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>暂无，但曾与上海电气有设备合作历史</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>REC Group、Heliene、Q CELLS</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>欧洲高端组件市场约2%，HJT细分领域约8%</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2025年获得欧盟3亿欧元补贴，扩大德国工厂产能至1.4GW</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Utility companies with solar portfolios</t>
+          <t>Solar installation companies (residential &amp; commercial)</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -1858,261 +2011,309 @@
           <t>Medium (100-1000)</t>
         </is>
       </c>
-      <c r="R16" s="3" t="n">
-        <v>75</v>
+      <c r="R16" s="5" t="n">
+        <v>55</v>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>Dutch energy supplier investing in solar parks, procures modules for their own projects.</t>
+          <t>Swiss-German solar manufacturer, but also installs and buys modules for projects.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Solahart Industries Pty Ltd</t>
+          <t>Soltec Energías Renovables, S.A.</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://www.solahart.com.au</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>https://www.soltec.com</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>穆尔西亚, 西班牙</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>约800人</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>约4.5亿欧元</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>设计、制造和供应太阳能跟踪器（单轴/双轴）及光伏电站整体解决方案，同时开发自有电站项目并出售电力。</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>需要采购高性能光伏组件（适配其跟踪器系统）、逆变器、汇流箱及电站监控通信设备。</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>寻找具有TÜV/CE认证、大容量产能、价格竞争力强、能配合项目交付周期并提供长期质保的中国组件和逆变器制造商。</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>西班牙, 意大利, 巴西, 智利, 墨西哥, 美国</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Array Technologies, Nextracker, PVH, Ideematec</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>全球跟踪器市场约5%（前五名）</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布与欧洲大型能源集团签订1.2GW跟踪器供应框架协议，并计划在巴西新建组件适配测试中心。</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Solar installation companies (residential &amp; commercial)</t>
+          <t>制造商/EPC/项目开发商</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>70</v>
+          <t>中型（年收入&lt;10亿欧元）</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>Major Australian solar hot water and PV installer, distributes modules through network.</t>
+          <t>其跟踪器项目通常捆绑采购组件，中国厂商可通过其供应链渠道进入南美和欧洲市场。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SolarEdge Technologies, Inc.</t>
+          <t>Acciona Energía Global, S.L.</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://www.solaredge.com</t>
+          <t>https://www.acciona-energia.com</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>米尔皮塔斯, 美国</t>
+          <t>马德里, 西班牙</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>约1,700人</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>约30亿美元</t>
+          <t>约35亿欧元</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>全球领先的智能逆变器与功率优化器制造商，提供直流优化逆变系统及储能解决方案，主要面向户用和工商业光伏市场。</t>
+          <t>全球领先的可再生能源独立发电商（IPP），开发、建设和运营风能、太阳能光伏及光热电站，并出售绿电和能源管理服务。</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>需要从中国采购功率半导体器件（IGBT/MOSFET）、变压器、电感、PCB电路板、散热件及精密结构件。</t>
+          <t>大规模采购光伏组件、集中式/组串式逆变器、变压器、储能系统（BESS）及电站运维备件。</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>寻找通过IATF16949认证、具备高可靠性电子制造能力的中国EMS/OEM代工厂，以及关键电子元器件供应商。</t>
+          <t>偏好具有全球交付经验、符合国际银行可融资性标准（如IEC、UL）、产能稳定且具备长期合作意愿的一线中国供应商。</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>美国、德国、荷兰、意大利、澳大利亚</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>在深圳设有研发中心，并在苏州设有代工合作工厂</t>
+          <t>西班牙, 美国, 澳大利亚, 智利, 墨西哥, 南非</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>暂无（但通过中国EPC和供应商采购）</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Enphase Energy、华为数字能源、SMA Solar</t>
+          <t>Iberdrola, Enel Green Power, EDP Renewables, NextEra Energy</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>全球户用逆变器市场份额约15%（北美第一）</t>
+          <t>全球可再生能源装机容量约12GW（全球前20 IPP）</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2025年，SolarEdge宣布推出新一代双向直流耦合储能逆变器，并加大在欧洲工商业市场的渠道布局。</t>
+          <t>2025年启动澳大利亚500MW光伏+储能项目，并宣布将加速在西班牙本土的组件回收合作计划。</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Solar installation companies (residential &amp; commercial)</t>
+          <t>IPP/电站投资商</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="n">
-        <v>65</v>
+          <t>大型（年收入&gt;10亿欧元）</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>Inverter maker, but also buys modules for complete system offerings.</t>
+          <t>中国供应商可通过其全球项目招标进入高门槛的欧美和澳洲市场，建立标杆案例。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Enphase Energy, Inc.</t>
+          <t>Clean Energy Council (Australia) - Member Companies</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://enphase.com</t>
+          <t>https://www.cleanenergycouncil.org.au</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>弗里蒙特，美国</t>
+          <t>墨尔本, 澳大利亚</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>约60人（协会本身）</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>约15亿美元</t>
+          <t>不适用（非营利协会）</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>全球领先的微型逆变器及智能能源管理系统供应商，产品覆盖户用和工商业光伏，配套电池和监控软件。</t>
+          <t>澳大利亚清洁能源行业最高行业机构，代表会员企业（包括开发商、制造商、零售商、安装商）进行政策倡导、行业认证和标准制定。</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>从中国采购IGBT功率模块、电容、PCB板等电子元器件，以及部分代工服务（EMS）。</t>
+          <t>作为协会，不直接采购，但其会员企业（如安装商和EPC）需要采购分布式光伏组件、逆变器、支架及储能产品。</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>寻找通过IATF16949认证、具备高可靠性电子制造能力的中国供应商，支持全球多基地交付。</t>
+          <t>为会员筛选符合澳大利亚CEC认证（Clean Energy Council Approved）的组件和逆变器供应商，要求产品通过严格测试并符合当地电网标准。</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>美国、荷兰、德国、澳大利亚、巴西</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>在深圳设有研发中心，与多家EMS代工厂合作</t>
+          <t>澳大利亚</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>暂无（但会员中大量采购中国品牌）</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>SolarEdge、SMA Solar、Huawei</t>
+          <t>Smart Energy Council, SolarQuotes（非直接竞争）</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>全球微型逆变器市场份额约45%，美国户用市场约55%</t>
+          <t>覆盖澳大利亚90%以上的清洁能源企业会员</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2025年推出IQ8P微逆，支持单块组件功率达480W，并进入日本市场</t>
+          <t>2025年发布新版组件和逆变器认证清单，新增多项针对中国产品的安全测试要求，并推动本土制造激励政策。</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Solar installation companies (residential &amp; commercial)</t>
+          <t>行业协会/标准制定者</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>澳大利亚</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R19" s="5" t="n">
-        <v>60</v>
+          <t>中型（协会，影响面广）</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Microinverter maker, but also buys modules for its own solar systems.</t>
+          <t>中国组件和逆变器厂商必须与其认证体系对接，通过其会员网络拓展澳洲分销渠道。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Meyer Burger Technology AG</t>
+          <t>Solahart Industries Pty Ltd</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://www.meyerburger.com</t>
+          <t>https://www.solahart.com.au</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2122,127 +2323,175 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>图恩，瑞士</t>
+          <t>悉尼, 澳大利亚</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>约500人</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>约2亿瑞士法郎</t>
+          <t>约2亿澳元</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>高端光伏组件制造商，主推异质结（HJT）技术，销售高效组件及光伏制造设备，聚焦欧洲本土生产。</t>
+          <t>澳大利亚老牌太阳能热水系统和光伏系统制造商与零售商，提供家用和商用屋顶光伏组件、逆变器及热泵解决方案，主要通过经销商网络销售。</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>从中国采购异质结电池片、银浆、靶材及部分辅材，同时采购逆变器用于配套销售。</t>
+          <t>采购高效单晶组件（450W+）、组串式逆变器（5-30kW）、储能电池及安装配件（支架、线缆）。</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>寻找具备HJT电池片量产能力、技术领先的中国供应商，要求长期稳定供应和共同研发意愿。</t>
+          <t>寻找具有CEC认证、品牌可贴牌（OEM）、质量稳定且能提供澳洲本地库存或快速物流的中国供应商。</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>德国、瑞士、奥地利、意大利、美国</t>
+          <t>澳大利亚, 新西兰, 太平洋岛国</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>暂无，但曾与上海电气有设备合作历史</t>
+          <t>暂无（主要从中国进口）</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>REC Group、Heliene、Q CELLS</t>
+          <t>Rheem, Dux, Tesla (Powerwall), JinkoSolar (零售渠道)</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>欧洲高端组件市场约2%，HJT细分领域约8%</t>
+          <t>澳大利亚屋顶光伏零售市场约8%（传统品牌）</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2025年获得欧盟3亿欧元补贴，扩大德国工厂产能至1.4GW</t>
+          <t>2025年推出与国产储能电池集成的家庭能源管理系统，并扩大在昆士兰的经销商网络。</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Solar installation companies (residential &amp; commercial)</t>
+          <t>品牌制造商/分销商</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>澳大利亚</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="n">
-        <v>55</v>
+          <t>中型（年收入&lt;5亿澳元）</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Swiss-German solar manufacturer, but also installs and buys modules for projects.</t>
+          <t>中国厂商可通过其成熟的澳洲零售渠道快速进入家庭光伏市场，且其OEM需求适合产能灵活的企业。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Clean Energy Council (Australia) - Member Companies</t>
+          <t>Greenchoice B.V.</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://www.cleanenergycouncil.org.au</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>https://www.greenchoice.nl</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>乌得勒支, 荷兰</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>约400人</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>约8亿欧元</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>荷兰领先的可持续能源供应商，向家庭和企业销售绿色电力、天然气，并提供太阳能光伏系统租赁和安装服务（通过合作伙伴）。</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>采购分布式光伏组件（全黑/高效）、组串式逆变器（单相/三相）、智能电表及户用储能系统，用于其租赁和安装项目。</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>偏好欧洲有库存、符合荷兰SDE++补贴要求、具备良好品牌声誉和售后支持的中国供应商，重视碳足迹认证。</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>荷兰, 比利时（部分）</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>暂无（通过欧洲分销商采购）</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Vandebron, Eneco, Essent, Budget Energie</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>荷兰家庭能源零售市场约5%（可持续能源细分领域前五）</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2025年扩大户用光伏租赁产品线，与荷兰安装商合作推出零首付方案，并计划增加储能捆绑销售。</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Solar installation companies (residential &amp; commercial)</t>
+          <t>能源零售商/光伏系统集成商</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>荷兰</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Small (&lt;100)</t>
-        </is>
-      </c>
-      <c r="R21" s="5" t="n">
-        <v>45</v>
+          <t>中型（年收入&lt;10亿欧元）</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Industry body, but many member installers buy Chinese modules for residential projects.</t>
+          <t>中国供应商可通过其渠道进入荷兰户用市场，且其注重可持续性和碳足迹，适合有绿色认证的产品。</t>
         </is>
       </c>
     </row>
